--- a/SRC_GUI_SelectorDataBuilder_E/Config/Config.xlsx
+++ b/SRC_GUI_SelectorDataBuilder_E/Config/Config.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0AB884-568B-448D-9AA4-EFA354D8B326}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622BCE0D-9699-432D-8DE6-582C79434266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9495" yWindow="-16710" windowWidth="22740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TargetInformation" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -87,7 +87,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -99,7 +99,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -110,7 +110,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -121,7 +121,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF8B008B"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -138,7 +138,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -149,7 +149,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -161,7 +161,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -172,7 +172,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -183,7 +183,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF8B008B"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -201,7 +201,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -212,7 +212,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF8B008B"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -229,7 +229,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -240,7 +240,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -252,7 +252,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -263,7 +263,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -274,7 +274,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF8B008B"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -291,7 +291,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -302,7 +302,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -314,7 +314,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -325,7 +325,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -336,7 +336,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF8B008B"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -353,7 +353,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -364,7 +364,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -376,7 +376,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -387,7 +387,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -398,7 +398,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF8B008B"/>
-        <rFont val="Yu Gothic"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -475,17 +475,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -493,7 +493,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF8B008B"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -501,7 +501,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -509,7 +509,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -518,7 +518,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -576,7 +576,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -855,18 +855,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.375" customWidth="1"/>
-    <col min="2" max="2" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="6.625" customWidth="1"/>
-    <col min="4" max="4" width="65" customWidth="1"/>
-    <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="68.5" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="74.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="68.42578125" customWidth="1"/>
     <col min="7" max="7" width="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -889,7 +889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -912,7 +912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -935,7 +935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -958,7 +958,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +981,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1027,11 +1027,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
